--- a/personal_forms/012_personal_finance_optimization_survey--personal_forms.xlsx
+++ b/personal_forms/012_personal_finance_optimization_survey--personal_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -538,53 +538,53 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>income</t>
+          <t>income_management</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>income</t>
+          <t>How do you manage your income?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>expenses</t>
+          <t>savings_frequency</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>expenses</t>
+          <t>How regularly do you save money?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,40 +594,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>financial_goals</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>What are your long term financial goals?</t>
-        </is>
-      </c>
+          <t>What are your long-term financial goals?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>investment_investments</t>
+          <t>financial_habits</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>investment</t>
+          <t>What are your money habits?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -639,19 +635,15 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>savings_routine</t>
+          <t>financial_planning_frequency</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>savings_routine</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>How regularly do you save money?</t>
-        </is>
-      </c>
+          <t>How often do you review your financial plan?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -661,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>financial_awareness</t>
+          <t>investment_strategy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>financial_awareness</t>
+          <t>What is your investment strategy?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -684,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>financial_planning</t>
+          <t>financial_planning_influence</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>financial_planning</t>
+          <t>Who influences your financial planning?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -707,27 +699,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>money_management</t>
+          <t>money_management_skills</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>money_management</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>How do you manage your money?</t>
-        </is>
-      </c>
+          <t>Which financial skill do you rate as your highest priority?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -739,19 +727,15 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>money_values</t>
+          <t>financial_stress</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>money_values</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>What is the source of your income?</t>
-        </is>
-      </c>
+          <t>How do you handle financial stress?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -761,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>emergency_fund</t>
+          <t>financial_education</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>emergency_fund</t>
+          <t>What is your approach to financial education?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -784,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>budgeting</t>
+          <t>follow_up_checkin</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>budgeting</t>
+          <t>How often do you perform a follow-up check on your finances?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -812,19 +796,15 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>money_management_skills</t>
+          <t>money_transfer</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>money_management_skills</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Which skill would you rate as your highest priority?</t>
-        </is>
-      </c>
+          <t>How do you transfer money?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -834,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>financial_stress</t>
+          <t>financial_planning_tools</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>financial_stress</t>
+          <t>What are your favorite financial planning tools?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -857,40 +837,40 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>financial_education</t>
+          <t>financial_support</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>financial_education</t>
+          <t>Do you have a financial support system in place?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>money_habits</t>
+          <t>financial_planning_frequency_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>money_habits</t>
+          <t>How often do you perform a financial planning check?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -903,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>financial_planning_tools</t>
+          <t>investment</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>financial_planning_tools</t>
+          <t>What is your investment approach?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -926,194 +906,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>financial_support</t>
+          <t>financial_planning_influence_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>financial_support</t>
+          <t>Financial Planning Influence 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>financial_planning_frequency</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>financial_planning_frequency</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>follow_up_checkin</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>follow_up_checkin</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>money_transfer</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>money_transfer</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>financial_planning_frequency</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>financial_planning_frequency</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>How often do you review your financial plan?</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>investment</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>investment</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>What is your investment strategy?</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>financial_planning_influence</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>financial_planning_influence</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Who influences your financial planning?</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>follow_up_checkin</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>follow_up_checkin</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1130,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="47" customWidth="1" min="2" max="2"/>
+    <col width="47" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1158,92 +965,92 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>financial_goals_choices</t>
+          <t>income_management_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>goal_1</t>
+          <t>savings</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Goal 1</t>
+          <t>Savings</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>financial_goals_choices</t>
+          <t>income_management_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>goal_2</t>
+          <t>investments</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Goal 2</t>
+          <t>Investments</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>financial_goals_choices</t>
+          <t>income_management_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>goal_3</t>
+          <t>salary</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Goal 3</t>
+          <t>Salary</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>financial_goals_choices</t>
+          <t>income_management_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>goal_4</t>
+          <t>inheritance</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Goal 4</t>
+          <t>Inheritance</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>financial_goals_choices</t>
+          <t>income_management_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>goal_5</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Goal 5</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>savings_routine_choices</t>
+          <t>savings_frequency_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1260,7 +1067,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>savings_routine_choices</t>
+          <t>savings_frequency_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1277,7 +1084,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>savings_routine_choices</t>
+          <t>savings_frequency_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1294,7 +1101,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>savings_routine_choices</t>
+          <t>savings_frequency_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1311,58 +1118,58 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>money_management_choices</t>
+          <t>financial_goals_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>saving_for_a_down_payment_on_a_house</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Saving for a down payment on a house</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>money_management_choices</t>
+          <t>financial_goals_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>credit_cards</t>
+          <t>retirement</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Credit cards</t>
+          <t>Retirement</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>money_management_choices</t>
+          <t>financial_goals_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>bank_account</t>
+          <t>paying_off_debt</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bank account</t>
+          <t>Paying off debt</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>money_management_choices</t>
+          <t>financial_goals_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1379,389 +1186,967 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>money_values_choices</t>
+          <t>financial_habits_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>savings</t>
+          <t>saving</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Savings</t>
+          <t>Saving</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>money_values_choices</t>
+          <t>financial_habits_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>investments</t>
+          <t>budgeting</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Investments</t>
+          <t>Budgeting</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>money_values_choices</t>
+          <t>financial_habits_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>salary</t>
+          <t>spending_less_than_earning</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Salary</t>
+          <t>Spending less than earning</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>money_values_choices</t>
+          <t>financial_habits_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>inheritance</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Inheritance</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>money_values_choices</t>
+          <t>financial_planning_frequency_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>money_management_skills_choices</t>
+          <t>financial_planning_frequency_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>budgeting</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Budgeting</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>money_management_skills_choices</t>
+          <t>financial_planning_frequency_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>time_management</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Time management</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>money_management_skills_choices</t>
+          <t>financial_planning_frequency_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>organization</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Organization</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>money_management_skills_choices</t>
+          <t>investment_strategy_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>prioritization</t>
+          <t>stocks</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Prioritization</t>
+          <t>Stocks</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>money_management_skills_choices</t>
+          <t>investment_strategy_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>bonds</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bonds</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>financial_planning_frequency_choices</t>
+          <t>investment_strategy_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>mutual_funds</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Mutual funds</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>financial_planning_frequency_choices</t>
+          <t>investment_strategy_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>real_estate</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>financial_planning_frequency_choices</t>
+          <t>investment_strategy_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>financial_planning_frequency_choices</t>
+          <t>financial_planning_influence_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>spouse_or_partner</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Spouse or partner</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>investment_choices</t>
+          <t>financial_planning_influence_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>stocks</t>
+          <t>family_or_friends</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Stocks</t>
+          <t>Family or friends</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>investment_choices</t>
+          <t>financial_planning_influence_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>bonds</t>
+          <t>financial_advisor</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bonds</t>
+          <t>Financial advisor</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>investment_choices</t>
+          <t>financial_planning_influence_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>mutual_funds</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Mutual funds</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>investment_choices</t>
+          <t>money_management_skills_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>real_estate</t>
+          <t>budgeting</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Real estate</t>
+          <t>Budgeting</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>investment_choices</t>
+          <t>money_management_skills_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Time management</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>financial_planning_influence_choices</t>
+          <t>money_management_skills_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>spouse_or_partner</t>
+          <t>organization</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spouse or partner</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>financial_planning_influence_choices</t>
+          <t>money_management_skills_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>family_or_friends</t>
+          <t>prioritization</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Family or friends</t>
+          <t>Prioritization</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>financial_planning_influence_choices</t>
+          <t>money_management_skills_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>financial_advisor</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Financial advisor</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>financial_planning_influence_choices</t>
+          <t>financial_stress_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>reduce_spending</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Reduce spending</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>financial_stress_choices</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>increase_income</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Increase income</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>financial_stress_choices</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>seek_help_from_a_professional</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Seek help from a professional</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>financial_stress_choices</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>other</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>financial_education_choices</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>reading_books</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Reading books</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>financial_education_choices</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>taking_courses</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Taking courses</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>financial_education_choices</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>seeking_advice_from_a_friend_or_family_member</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Seeking advice from a friend or family member</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>financial_education_choices</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>follow_up_checkin_choices</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>follow_up_checkin_choices</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>follow_up_checkin_choices</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>follow_up_checkin_choices</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>money_transfer_choices</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>money_transfer_choices</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>in_person</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>In person</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>money_transfer_choices</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>mobile_transfer</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Mobile transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>money_transfer_choices</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>financial_planning_tools_choices</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>spreadsheets</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Spreadsheets</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>financial_planning_tools_choices</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>budgeting_apps</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Budgeting apps</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>financial_planning_tools_choices</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>financial_advisors</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Financial advisors</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>financial_planning_tools_choices</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>financial_support_choices</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>financial_support_choices</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>financial_planning_frequency_2_choices</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>financial_planning_frequency_2_choices</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>financial_planning_frequency_2_choices</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>financial_planning_frequency_2_choices</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>investment_choices</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>stocks</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Stocks</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>investment_choices</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>bonds</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Bonds</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>investment_choices</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>mutual_funds</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Mutual funds</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>investment_choices</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>real_estate</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Real estate</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>investment_choices</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>financial_planning_influence_2_choices</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>spouse_or_partner</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Spouse or partner</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>financial_planning_influence_2_choices</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>family_or_friends</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Family or friends</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>financial_planning_influence_2_choices</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>financial_advisor</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Financial advisor</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>financial_planning_influence_2_choices</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
